--- a/results/Int All Data 0.4/Rando_1_permute.xlsx
+++ b/results/Int All Data 0.4/Rando_1_permute.xlsx
@@ -440,1017 +440,1017 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7039784308160685</v>
+        <v>0.6945032121571764</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7068938827111122</v>
+        <v>0.6945032121571764</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7068938827111122</v>
+        <v>0.6949160195051471</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7068938827111122</v>
+        <v>0.6905428416625816</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7068938827111122</v>
+        <v>0.6905428416625816</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6845184344281328</v>
+        <v>0.6905428416625816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6791003379860161</v>
+        <v>0.6908588972883717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6739015454475089</v>
+        <v>0.6908588972883717</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6765976934389433</v>
+        <v>0.6905428416625816</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6765976934389433</v>
+        <v>0.6908588972883717</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6769137490647333</v>
+        <v>0.6920005676101034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6769137490647333</v>
+        <v>0.6920005676101034</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6769137490647333</v>
+        <v>0.6920005676101034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6621429861451533</v>
+        <v>0.6920005676101034</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6512100415387394</v>
+        <v>0.6920005676101034</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6512100415387394</v>
+        <v>0.6920005676101034</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6532998787378415</v>
+        <v>0.6963737454526691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6540287417116024</v>
+        <v>0.6963737454526691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6499716194948271</v>
+        <v>0.6963737454526691</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6492427565210661</v>
+        <v>0.6963737454526691</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6470561675997832</v>
+        <v>0.6963737454526691</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6470561675997832</v>
+        <v>0.6960576898268789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6562153306328853</v>
+        <v>0.6975154157744008</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6546350525039346</v>
+        <v>0.6957416342010887</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6546350525039346</v>
+        <v>0.6954255785752986</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6637942155370365</v>
+        <v>0.6943806599757476</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6645230785107975</v>
+        <v>0.6951095229495086</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6645230785107975</v>
+        <v>0.6951095229495086</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6659808044583193</v>
+        <v>0.6935550452798059</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6711795969968265</v>
+        <v>0.6928261823060451</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6719084599705875</v>
+        <v>0.6928261823060451</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6638909672592173</v>
+        <v>0.6925101266802549</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6642070228850074</v>
+        <v>0.6928261823060451</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6649358858587683</v>
+        <v>0.6928261823060451</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.667122474780051</v>
+        <v>0.6935550452798059</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6652519414845585</v>
+        <v>0.6950127712273279</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6630653525632757</v>
+        <v>0.6968833045228204</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6630653525632757</v>
+        <v>0.6986570860961325</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6658840527361387</v>
+        <v>0.6986570860961325</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6680706416574215</v>
+        <v>0.7008436750174153</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6687995046311824</v>
+        <v>0.6498490673133982</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6687995046311824</v>
+        <v>0.6498490673133982</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6680706416574215</v>
+        <v>0.6643747258701205</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6744111045176604</v>
+        <v>0.6638135658814727</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6726373229443484</v>
+        <v>0.6593887871204107</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6669031708764417</v>
+        <v>0.6562540313217575</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6657615005547098</v>
+        <v>0.6565700869475477</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6657615005547098</v>
+        <v>0.6536288345932557</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6657615005547098</v>
+        <v>0.6525839159937047</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6657615005547098</v>
+        <v>0.6541641941226554</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6669031708764417</v>
+        <v>0.6507843339611445</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6778812662865399</v>
+        <v>0.648204288036327</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6774684589385691</v>
+        <v>0.6450437317784257</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6692252122087773</v>
+        <v>0.6439988131788745</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6727985758146495</v>
+        <v>0.6362909259784824</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6766621945870637</v>
+        <v>0.640812456461725</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6753721716246549</v>
+        <v>0.6401803452101447</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6726566732887845</v>
+        <v>0.6401803452101447</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6757914290874377</v>
+        <v>0.6344913439459222</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6676771846538868</v>
+        <v>0.6329368662762197</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6601950514719162</v>
+        <v>0.6275639206377873</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.653654635052504</v>
+        <v>0.6236035501431926</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6533385794267138</v>
+        <v>0.6149732965246781</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6542867463040842</v>
+        <v>0.6142444335509172</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6540674424004747</v>
+        <v>0.6126641554219665</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6484300420547485</v>
+        <v>0.6198624835522072</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6464627570370752</v>
+        <v>0.6161214169612219</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6509133362573853</v>
+        <v>0.6145411388322712</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6502812250058051</v>
+        <v>0.6139090275806909</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6540738925152868</v>
+        <v>0.6139090275806909</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6528096700121262</v>
+        <v>0.6139090275806909</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6529064217343068</v>
+        <v>0.6176307438272401</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6529064217343068</v>
+        <v>0.6190884697747621</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6538287881524292</v>
+        <v>0.6190884697747621</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6677223354575712</v>
+        <v>0.6066655486467659</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6735080884439744</v>
+        <v>0.6123287494517402</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.640077143373152</v>
+        <v>0.6070525555354885</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6380840578962306</v>
+        <v>0.6041564539848809</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.63798730617405</v>
+        <v>0.6024407234448773</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6389354730514203</v>
+        <v>0.5941781263706494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6418251244872158</v>
+        <v>0.5896049949689104</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6366908330968292</v>
+        <v>0.5896049949689104</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6413800665651849</v>
+        <v>0.5905531618462809</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6413800665651849</v>
+        <v>0.5839546943935602</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6466756108258727</v>
+        <v>0.5313927087902165</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6457532444077505</v>
+        <v>0.5604956268221575</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6351750561159988</v>
+        <v>0.5300123842204392</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6394256817771357</v>
+        <v>0.5406163729714388</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6136123222993369</v>
+        <v>0.5360432415697</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6227779354472509</v>
+        <v>0.4628279883381924</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6216685156995794</v>
+        <v>0.4514435356949354</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6210364044479992</v>
+        <v>0.4593642766841249</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6214556619107821</v>
+        <v>0.4773342965504786</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6138703268918186</v>
+        <v>0.4913826466111097</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6219974715549936</v>
+        <v>0.4571905879924663</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6268608581232746</v>
+        <v>0.4393108697334812</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5463698753837818</v>
+        <v>0.460847803090895</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.552458783766351</v>
+        <v>0.4627763874196961</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5414097370933203</v>
+        <v>0.4666142057328621</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4745220464924276</v>
+        <v>0.4665884052736138</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4498955081400449</v>
+        <v>0.4652274310482727</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4475605665780851</v>
+        <v>0.4652274310482727</v>
       </c>
     </row>
     <row r="104">
@@ -1460,127 +1460,127 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4511855311024536</v>
+        <v>0.4741027890296447</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.451540287417116</v>
+        <v>0.4483861812740267</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.447547666348461</v>
+        <v>0.4228308263887097</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4437549988389793</v>
+        <v>0.4411878531437859</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4437549988389793</v>
+        <v>0.4426455790913079</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.449605252973503</v>
+        <v>0.4412394540622823</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.449605252973503</v>
+        <v>0.440607342810702</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.454500890115844</v>
+        <v>0.4688588456874533</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4593384762248768</v>
+        <v>0.4688588456874533</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4593384762248768</v>
+        <v>0.4417941639361181</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4551072009081761</v>
+        <v>0.4417941639361181</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4575453443071287</v>
+        <v>0.452565855672231</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4571260868443459</v>
+        <v>0.4518627931577182</v>
       </c>
     </row>
     <row r="117">
@@ -1590,397 +1590,397 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4538429784050156</v>
+        <v>0.4026742176010733</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4513145333986945</v>
+        <v>0.4042222451559637</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4346796872984339</v>
+        <v>0.4088792280502593</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5067468200933977</v>
+        <v>0.4088792280502593</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4833200030960552</v>
+        <v>0.4609058541242034</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.479753089604995</v>
+        <v>0.4609058541242034</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4570357852369772</v>
+        <v>0.4581452049846487</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.454191284604866</v>
+        <v>0.4858613483320003</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4611316081426249</v>
+        <v>0.4541525839159937</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4689039964911376</v>
+        <v>0.4490053922959829</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4624925823679661</v>
+        <v>0.4490053922959829</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4651113289816559</v>
+        <v>0.456113418818855</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4221793647926934</v>
+        <v>0.4548491963156944</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4113754224825202</v>
+        <v>0.4473090121004154</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4178061869501277</v>
+        <v>0.4528109600350886</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4228243762738977</v>
+        <v>0.4495988028586909</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4180254908537372</v>
+        <v>0.4432518898836399</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4233661859181094</v>
+        <v>0.4484958332258314</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4197025207048685</v>
+        <v>0.4494440001032018</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4042286952707758</v>
+        <v>0.4640406099228567</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.410162800897856</v>
+        <v>0.4737351324853582</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.410162800897856</v>
+        <v>0.4737351324853582</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4093113857426662</v>
+        <v>0.4831587502257541</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4116076266157537</v>
+        <v>0.4805335534972522</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4116076266157537</v>
+        <v>0.4772826956319823</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.503979720839031</v>
+        <v>0.4765280321989732</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.503979720839031</v>
+        <v>0.4765280321989732</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5071918780154286</v>
+        <v>0.4773213963208545</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4974715549936789</v>
+        <v>0.4774245981578472</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4961363812275859</v>
+        <v>0.4959428777832245</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4969813462679636</v>
+        <v>0.497052297530896</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4970780979901442</v>
+        <v>0.5041925746278284</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4979811140638303</v>
+        <v>0.5038765190020382</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4986132253154106</v>
+        <v>0.5076240357078357</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4986132253154106</v>
+        <v>0.5050955907015144</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4986132253154106</v>
+        <v>0.5017673314584999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4986132253154106</v>
+        <v>0.5040055212982791</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4986132253154106</v>
+        <v>0.5045408808276788</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4986132253154106</v>
+        <v>0.5005224592997756</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5007030625145128</v>
+        <v>0.5011739208957919</v>
       </c>
     </row>
   </sheetData>
